--- a/RESTORATION_kobo_data_latest.xlsx
+++ b/RESTORATION_kobo_data_latest.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BZ25"/>
+  <dimension ref="A1:CA25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -366,370 +366,375 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>site_type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>restoration_site</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>restoration_site/nursery_kirui</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>restoration_site/transplanting_kirui_shangani</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>restoration_site/transplanting_kirui_corner</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>restoration_site/transplanting_kirui_exp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>restoration_site/nursery_kigombe</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>restoration_site/transplanting_kigombe_taa</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>restoration_site/transplanting_kigome_makome</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>restoration_site/nursery_msuka</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>restoration_site/transplanting_msuka_panga_punge</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>restoration_team</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>restoration_team/shabani</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>restoration_team/burhani</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>restoration_team/phares</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>restoration_team/adam</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>restoration_team/yusuf</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>restoration_team/omary</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>restoration_team/nusra</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>restoration_team/gerad</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>restoration_team/abbakar</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>restoration_team/jean</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>restoration_team/pagu</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>restoration_team/jumbe</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>restoration_team/mwindadi</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>restoration_team/athumani</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>restoration_team/ben</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>restoration_team/mbarouk_hamad</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>restoration_team/rashid_said</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>restoration_team/hemeduni_abdalla</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>number_of_other_participants</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Start_time</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>End_time</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>tide</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Site_depth</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>water_temperature</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>water_clarity</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>select_activity</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>select_activity/fragmentation</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>select_activity/transplantation</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>select_activity/monitoring</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>select_activity/cleaning_and_maintaining</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>number_of_fragments_on_tables</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>number_of_tables_installed</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>number_of_fragments_transplanted</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>number_of_reef_stars_installed</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>number_of_reef_stars_installed_001</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>number_of_fence_wires_installed</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>number_of_fence_wires_installe</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>number_of_fence_wires_installe_001</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>number_of_tables_monitored</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>number_of_tables_cleaned</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>total_tables_on_nursery_to_date</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>total_fragments_on_nursery_to_date</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>total_fragments_deployed_to_date</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>total_reef_starts_deployed_to_date</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>total_reef_starts_deployed_to_</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>total_fence_wires_deployed_to_date</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>total_fence_wires_deployed_to_</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>total_fragments_transpalated_to_date</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>Remacks_comments_observations</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>Add_photos</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>Add_video</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>_id</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>_uuid</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>_submission_time</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>_validation_status</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>_notes</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>_status</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>_submitted_by</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>__version__</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>_tags</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>meta/rootUuid</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>_index</t>
         </is>
@@ -758,17 +763,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>nursery</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>nursery_kirui</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -808,14 +813,14 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>phares adam yusuf omary nusra hemeduni_abdalla</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>0</t>
@@ -823,7 +828,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -848,7 +853,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -898,59 +903,59 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>09:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>01:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>falling</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>cleaning_and_maintaining</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR2" t="inlineStr">
         <is>
           <t>0</t>
@@ -963,88 +968,93 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>10520</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>2249</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>305</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>3965</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>9714</t>
         </is>
       </c>
-      <c r="BP2">
+      <c r="BQ2">
         <v>803631047</v>
       </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>579336da-6c8e-4fc1-98f7-ff8ace9a965d</t>
-        </is>
-      </c>
       <c r="BR2" t="inlineStr">
         <is>
+          <t>723c6a83-f234-4435-960a-bb9dc3480fa6</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
           <t>2026-07-06T17:14:31</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>v55AV6dH7kjPAvdHKtEVVG</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>uuid:eb086f57-a704-4efc-a15a-f61cc9de615b</t>
         </is>
       </c>
-      <c r="BZ2">
+      <c r="CA2">
         <v>1</v>
       </c>
     </row>
@@ -1071,17 +1081,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>nursery</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>nursery_kirui</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1121,14 +1131,14 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>phares adam yusuf omary nusra hemeduni_abdalla</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1136,7 +1146,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1161,7 +1171,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1211,62 +1221,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
         <is>
           <t>11:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>14:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>falling</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>fragmentation</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1281,93 +1291,98 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>10688</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>2249</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>305</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>3965</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>9714</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>Transplanted started at April,2026 for Kirui Shangani and May,2026 for Kirui corner</t>
         </is>
       </c>
-      <c r="BP3">
+      <c r="BQ3">
         <v>805337414</v>
       </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>81e06e4e-2c8d-423a-9066-8acdd02fff7c</t>
-        </is>
-      </c>
       <c r="BR3" t="inlineStr">
         <is>
+          <t>e92153d7-1cf6-44a3-9e8e-3a20d9d3c999</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
           <t>2026-07-08T13:21:52</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>vCkHvrKwcRQ5DbaMoYkkd6</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>uuid:81e06e4e-2c8d-423a-9066-8acdd02fff7c</t>
         </is>
       </c>
-      <c r="BZ3">
+      <c r="CA3">
         <v>2</v>
       </c>
     </row>
@@ -1394,17 +1409,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>nursery</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>nursery_kirui</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1444,14 +1459,14 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>phares adam yusuf omary nusra hemeduni_abdalla</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1459,7 +1474,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1484,7 +1499,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1534,7 +1549,7 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1544,52 +1559,52 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
         <is>
           <t>10:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>13:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>falling</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>fragmentation</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1604,93 +1619,98 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="AV4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>10968</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>2249</t>
         </is>
       </c>
-      <c r="BH4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>305</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>3965</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>9714</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>P5060091-17_48_57.JPG</t>
         </is>
       </c>
-      <c r="BP4">
+      <c r="BQ4">
         <v>806506452</v>
       </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>a2f65acf-c7f4-4edf-afae-93e5ae116b85</t>
-        </is>
-      </c>
       <c r="BR4" t="inlineStr">
         <is>
+          <t>63f04db7-3dd1-4f1d-aba6-944e393dc9bb</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
           <t>2026-07-09T14:52:46</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>vqNFtU5FCbU6qmGgWH2f6a</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>uuid:22730a20-cf8d-4fa7-a94a-4eb023d8da89</t>
         </is>
       </c>
-      <c r="BZ4">
+      <c r="CA4">
         <v>3</v>
       </c>
     </row>
@@ -1717,17 +1737,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>nursery</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>nursery_kirui</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1767,14 +1787,14 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>phares adam yusuf omary nusra hemeduni_abdalla</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1782,7 +1802,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1807,7 +1827,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1857,62 +1877,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
         <is>
           <t>10:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>16:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>falling</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>fragmentation</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1927,93 +1947,98 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
           <t>784</t>
         </is>
       </c>
-      <c r="AV5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>11752</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>2249</t>
         </is>
       </c>
-      <c r="BH5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>305</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>3965</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>9714</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>P5080108-17_50_58.JPG</t>
         </is>
       </c>
-      <c r="BP5">
+      <c r="BQ5">
         <v>807657551</v>
       </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>5c2914a0-3db5-467a-b1a7-4272176d5b12</t>
-        </is>
-      </c>
       <c r="BR5" t="inlineStr">
         <is>
+          <t>3a63efd5-713e-4387-9ebe-28551474b610</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
           <t>2026-07-10T14:52:06</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>vqNFtU5FCbU6qmGgWH2f6a</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>uuid:65f95ea3-ee4c-44bc-bed9-156549361a9d</t>
         </is>
       </c>
-      <c r="BZ5">
+      <c r="CA5">
         <v>4</v>
       </c>
     </row>
@@ -2040,14 +2065,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>transplanting</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>transplanting_kigome_makome</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2075,12 +2100,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -2090,14 +2115,14 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>abbakar jumbe mwindadi athumani</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2135,12 +2160,12 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2150,7 +2175,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2165,7 +2190,7 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2185,62 +2210,62 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>12:45:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>15:45:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>rising</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>transplantation</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
@@ -2248,16 +2273,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2265,49 +2290,49 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BB6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>12432</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>24013</t>
         </is>
       </c>
-      <c r="BH6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>2704</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2315,48 +2340,53 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
           <t>26717</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="BP6">
+      <c r="BQ6">
         <v>809373757</v>
       </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>aa8f08e0-9321-4d16-a158-baaa6c5a7454</t>
-        </is>
-      </c>
       <c r="BR6" t="inlineStr">
         <is>
+          <t>b8ce9a44-60c5-4922-af43-156e29bfba7e</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
           <t>2026-07-13T09:52:22</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>vqNFtU5FCbU6qmGgWH2f6a</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>uuid:aa8f08e0-9321-4d16-a158-baaa6c5a7454</t>
         </is>
       </c>
-      <c r="BZ6">
+      <c r="CA6">
         <v>5</v>
       </c>
     </row>
@@ -2381,16 +2411,11 @@
           <t>kigombe</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>abbakar jumbe mwindadi athumani</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>0</t>
@@ -2428,12 +2453,12 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2443,7 +2468,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2458,7 +2483,7 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2483,49 +2508,49 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>08:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>13:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>rising</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AP7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>cleaning_and_maintaining</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR7" t="inlineStr">
         <is>
           <t>0</t>
@@ -2538,44 +2563,44 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>12432</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>24013</t>
         </is>
       </c>
-      <c r="BH7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>2704</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK7" t="inlineStr">
         <is>
           <t>0</t>
@@ -2583,48 +2608,53 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
           <t>26727</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="BP7">
+      <c r="BQ7">
         <v>809385709</v>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>43a37268-be3c-440c-9f9a-511ed27f39eb</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2026-07-13T10:03:26</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>vqNFtU5FCbU6qmGgWH2f6a</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>uuid:43a37268-be3c-440c-9f9a-511ed27f39eb</t>
         </is>
       </c>
-      <c r="BZ7">
+      <c r="CA7">
         <v>6</v>
       </c>
     </row>
@@ -2651,14 +2681,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>transplanting</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>transplanting_kigombe_taa</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>0</t>
@@ -2681,12 +2711,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -2701,14 +2731,14 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>abbakar jumbe mwindadi athumani</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>0</t>
@@ -2746,12 +2776,12 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2761,7 +2791,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2801,49 +2831,49 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>10:15:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>15:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>rising</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AP8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>cleaning_and_maintaining</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR8" t="inlineStr">
         <is>
           <t>0</t>
@@ -2856,44 +2886,44 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>12432</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>24013</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>2704</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK8" t="inlineStr">
         <is>
           <t>0</t>
@@ -2901,48 +2931,53 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
           <t>26717</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="BP8">
+      <c r="BQ8">
         <v>809390319</v>
       </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>8e1528e9-df26-4dc4-a323-f28fa2409672</t>
-        </is>
-      </c>
       <c r="BR8" t="inlineStr">
         <is>
+          <t>38ee1eb4-06df-4080-84c4-ec201dda3e8f</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
           <t>2026-07-13T10:07:16</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>vqNFtU5FCbU6qmGgWH2f6a</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>uuid:8e1528e9-df26-4dc4-a323-f28fa2409672</t>
         </is>
       </c>
-      <c r="BZ8">
+      <c r="CA8">
         <v>7</v>
       </c>
     </row>
@@ -2969,14 +3004,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>transplanting</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>transplanting_kigombe_taa</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2999,12 +3034,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3019,14 +3054,14 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>abbakar jumbe mwindadi athumani</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3064,12 +3099,12 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -3079,7 +3114,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3094,7 +3129,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -3119,49 +3154,49 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
         <is>
           <t>09:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>14:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>rising</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>cleaning_and_maintaining</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3174,44 +3209,44 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>12432</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>24013</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>2704</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3219,48 +3254,53 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
           <t>26717</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="BP9">
+      <c r="BQ9">
         <v>809394701</v>
       </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>8e4ea9ed-2706-4f45-abd8-83647806c8dd</t>
-        </is>
-      </c>
       <c r="BR9" t="inlineStr">
         <is>
+          <t>4261bdc6-98b5-48d7-b8d5-5857319ce592</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
           <t>2026-07-13T10:11:06</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>vqNFtU5FCbU6qmGgWH2f6a</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>uuid:8e4ea9ed-2706-4f45-abd8-83647806c8dd</t>
         </is>
       </c>
-      <c r="BZ9">
+      <c r="CA9">
         <v>8</v>
       </c>
     </row>
@@ -3287,14 +3327,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>transplanting</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>nursery_kirui transplanting_kirui_shangani</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>1</t>
@@ -3302,7 +3342,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3337,14 +3377,14 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>adam yusuf omary nusra pagu hemeduni_abdalla</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>0</t>
@@ -3357,7 +3397,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -3377,7 +3417,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -3392,12 +3432,12 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -3427,62 +3467,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
         <is>
           <t>09:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>15:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>falling</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AP10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>fragmentation</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -3497,98 +3537,103 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="AV10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>11164</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>2249</t>
         </is>
       </c>
-      <c r="BH10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>305</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>3965</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BL10" t="inlineStr">
         <is>
           <t>3500</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>9714</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>P5100134-17_11_20.JPG</t>
         </is>
       </c>
-      <c r="BP10">
+      <c r="BQ10">
         <v>809892839</v>
       </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>90c08df0-f81e-4a47-a016-6ff87b2ba120</t>
-        </is>
-      </c>
       <c r="BR10" t="inlineStr">
         <is>
+          <t>d5b7962a-390d-46b4-99f0-38c87b2fe178</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
           <t>2026-07-13T17:11:32</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>vqNFtU5FCbU6qmGgWH2f6a</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>uuid:90c08df0-f81e-4a47-a016-6ff87b2ba120</t>
         </is>
       </c>
-      <c r="BZ10">
+      <c r="CA10">
         <v>9</v>
       </c>
     </row>
@@ -3615,14 +3660,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>nursery</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>nursery_msuka</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>0</t>
@@ -3655,32 +3700,32 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>burhani mbarouk_hamad rashid_said</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -3745,7 +3790,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -3755,7 +3800,7 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -3765,49 +3810,49 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AK11" t="inlineStr">
         <is>
           <t>09:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>15:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>rising</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AP11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>cleaning_and_maintaining</t>
         </is>
       </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR11" t="inlineStr">
         <is>
           <t>0</t>
@@ -3820,44 +3865,44 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>15271</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>5373</t>
         </is>
       </c>
-      <c r="BH11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>3120</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK11" t="inlineStr">
         <is>
           <t>0</t>
@@ -3865,48 +3910,53 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
           <t>8493</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>we are planning to make transplanting and fragmentation in this month of July</t>
         </is>
       </c>
-      <c r="BP11">
+      <c r="BQ11">
         <v>810629008</v>
       </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>726de242-1057-4ae0-8f70-7e85ae64d4ee</t>
-        </is>
-      </c>
       <c r="BR11" t="inlineStr">
         <is>
+          <t>1f798809-4836-4b16-b5fa-4c1951596259</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
           <t>2026-07-14T11:08:57</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>vCkHvrKwcRQ5DbaMoYkkd6</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>uuid:a93e9bf5-9324-4d75-90bd-b552ac7eec9e</t>
         </is>
       </c>
-      <c r="BZ11">
+      <c r="CA11">
         <v>10</v>
       </c>
     </row>
@@ -3933,14 +3983,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>transplanting</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>transplanting_msuka_panga_punge</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>0</t>
@@ -3978,19 +4028,19 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>shabani burhani</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>1</t>
@@ -3998,7 +4048,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -4083,57 +4133,57 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AK12" t="inlineStr">
         <is>
           <t>08:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>16:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>rising</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AP12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>transplantation</t>
         </is>
       </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
@@ -4141,16 +4191,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
         <is>
           <t>500</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>0</t>
@@ -4158,49 +4208,49 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
           <t>500</t>
         </is>
       </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BB12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>15271</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>5873</t>
         </is>
       </c>
-      <c r="BH12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>3250</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK12" t="inlineStr">
         <is>
           <t>0</t>
@@ -4208,48 +4258,53 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
           <t>9123</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>The transplanting activities going on though we have challenge of epoxy for fragmentation</t>
         </is>
       </c>
-      <c r="BP12">
+      <c r="BQ12">
         <v>810679559</v>
       </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>e3e2e2d0-c008-4e26-a706-3b66836a23df</t>
-        </is>
-      </c>
       <c r="BR12" t="inlineStr">
         <is>
+          <t>b17cca2a-40a2-458c-8168-1168eb65d3d6</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
           <t>2026-07-14T11:55:04</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>vqNFtU5FCbU6qmGgWH2f6a</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>uuid:80fe4fd5-afa2-4238-8caa-700b4d003f9a</t>
         </is>
       </c>
-      <c r="BZ12">
+      <c r="CA12">
         <v>11</v>
       </c>
     </row>
@@ -4276,14 +4331,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>transplanting</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>nursery_kirui transplanting_kirui_shangani</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>1</t>
@@ -4291,7 +4346,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -4326,14 +4381,14 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>adam yusuf omary nusra hemeduni_abdalla</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>0</t>
@@ -4346,7 +4401,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -4366,7 +4421,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -4416,59 +4471,59 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AK13" t="inlineStr">
         <is>
           <t>09:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr">
+      <c r="AL13" t="inlineStr">
         <is>
           <t>14:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL13" t="inlineStr">
+      <c r="AM13" t="inlineStr">
         <is>
           <t>falling</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AN13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AO13" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
+      <c r="AP13" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AP13" t="inlineStr">
+      <c r="AQ13" t="inlineStr">
         <is>
           <t>fragmentation transplantation</t>
         </is>
       </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AR13" t="inlineStr">
         <is>
           <t>1</t>
@@ -4476,7 +4531,7 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
@@ -4486,24 +4541,24 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="AV13" t="inlineStr">
+      <c r="AW13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AW13" t="inlineStr">
+      <c r="AX13" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
@@ -4516,93 +4571,98 @@
       </c>
       <c r="BA13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="BB13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>178</t>
         </is>
       </c>
-      <c r="BE13" t="inlineStr">
+      <c r="BF13" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>11248</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
+      <c r="BH13" t="inlineStr">
         <is>
           <t>2249</t>
         </is>
       </c>
-      <c r="BH13" t="inlineStr">
+      <c r="BI13" t="inlineStr">
         <is>
           <t>305</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="BJ13" t="inlineStr">
         <is>
           <t>3965</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BK13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BL13" t="inlineStr">
         <is>
           <t>3678</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr">
+      <c r="BM13" t="inlineStr">
         <is>
           <t>9892</t>
         </is>
       </c>
-      <c r="BM13" t="inlineStr">
+      <c r="BN13" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="BP13">
+      <c r="BQ13">
         <v>810853924</v>
       </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>e9cbce53-1311-411d-91db-4bca321a400b</t>
-        </is>
-      </c>
       <c r="BR13" t="inlineStr">
         <is>
+          <t>62a31b1e-5c19-4c9d-a71e-7da2277c8bca</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
           <t>2026-07-14T14:38:26</t>
         </is>
       </c>
-      <c r="BU13" t="inlineStr">
+      <c r="BV13" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV13" t="inlineStr">
+      <c r="BW13" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW13" t="inlineStr">
+      <c r="BX13" t="inlineStr">
         <is>
           <t>vqNFtU5FCbU6qmGgWH2f6a</t>
         </is>
       </c>
-      <c r="BY13" t="inlineStr">
+      <c r="BZ13" t="inlineStr">
         <is>
           <t>uuid:e9cbce53-1311-411d-91db-4bca321a400b</t>
         </is>
       </c>
-      <c r="BZ13">
+      <c r="CA13">
         <v>12</v>
       </c>
     </row>
@@ -4629,14 +4689,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>nursery</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>nursery_msuka</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>0</t>
@@ -4669,24 +4729,24 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
           <t>shabani burhani</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>1</t>
@@ -4694,7 +4754,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -4779,49 +4839,49 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
+      <c r="AK14" t="inlineStr">
         <is>
           <t>07:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK14" t="inlineStr">
+      <c r="AL14" t="inlineStr">
         <is>
           <t>21:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
+      <c r="AM14" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
+      <c r="AN14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
+      <c r="AO14" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr">
+      <c r="AP14" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AP14" t="inlineStr">
+      <c r="AQ14" t="inlineStr">
         <is>
           <t>cleaning_and_maintaining</t>
         </is>
       </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR14" t="inlineStr">
         <is>
           <t>0</t>
@@ -4834,44 +4894,44 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="BE14" t="inlineStr">
+      <c r="BF14" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="BF14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>15271</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr">
+      <c r="BH14" t="inlineStr">
         <is>
           <t>5373</t>
         </is>
       </c>
-      <c r="BH14" t="inlineStr">
+      <c r="BI14" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="BI14" t="inlineStr">
+      <c r="BJ14" t="inlineStr">
         <is>
           <t>3120</t>
         </is>
       </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK14" t="inlineStr">
         <is>
           <t>0</t>
@@ -4879,48 +4939,53 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
           <t>8493</t>
         </is>
       </c>
-      <c r="BM14" t="inlineStr">
+      <c r="BN14" t="inlineStr">
         <is>
           <t>Cleaning and maintenance still going on due availability of dusts and algae on the tables</t>
         </is>
       </c>
-      <c r="BP14">
+      <c r="BQ14">
         <v>810990369</v>
       </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>ef8b318e-f531-4741-8957-af8caeddc6aa</t>
-        </is>
-      </c>
       <c r="BR14" t="inlineStr">
         <is>
+          <t>8beb7b51-d9f6-4508-9e0b-8742c165e847</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
           <t>2026-07-14T16:36:02</t>
         </is>
       </c>
-      <c r="BU14" t="inlineStr">
+      <c r="BV14" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV14" t="inlineStr">
+      <c r="BW14" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW14" t="inlineStr">
+      <c r="BX14" t="inlineStr">
         <is>
           <t>vqNFtU5FCbU6qmGgWH2f6a</t>
         </is>
       </c>
-      <c r="BY14" t="inlineStr">
+      <c r="BZ14" t="inlineStr">
         <is>
           <t>uuid:a8de2c7a-a5b6-4775-adf7-7cc7daf8806c</t>
         </is>
       </c>
-      <c r="BZ14">
+      <c r="CA14">
         <v>13</v>
       </c>
     </row>
@@ -4947,14 +5012,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>nursery</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>nursery_msuka</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>0</t>
@@ -4987,24 +5052,24 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
           <t>shabani burhani</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>1</t>
@@ -5012,7 +5077,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -5097,49 +5162,49 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
+      <c r="AK15" t="inlineStr">
         <is>
           <t>07:45:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK15" t="inlineStr">
+      <c r="AL15" t="inlineStr">
         <is>
           <t>15:45:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL15" t="inlineStr">
+      <c r="AM15" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
+      <c r="AN15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr">
+      <c r="AP15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr">
+      <c r="AQ15" t="inlineStr">
         <is>
           <t>cleaning_and_maintaining</t>
         </is>
       </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR15" t="inlineStr">
         <is>
           <t>0</t>
@@ -5152,44 +5217,44 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="BE15" t="inlineStr">
+      <c r="BF15" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="BF15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>15271</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr">
+      <c r="BH15" t="inlineStr">
         <is>
           <t>5373</t>
         </is>
       </c>
-      <c r="BH15" t="inlineStr">
+      <c r="BI15" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="BI15" t="inlineStr">
+      <c r="BJ15" t="inlineStr">
         <is>
           <t>3120</t>
         </is>
       </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK15" t="inlineStr">
         <is>
           <t>0</t>
@@ -5197,48 +5262,53 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
           <t>8493</t>
         </is>
       </c>
-      <c r="BM15" t="inlineStr">
+      <c r="BN15" t="inlineStr">
         <is>
           <t>Cleaning and maintenance going on due to presences of dusts and algae on the tables and fragments</t>
         </is>
       </c>
-      <c r="BP15">
+      <c r="BQ15">
         <v>810996729</v>
       </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>5e5ab4ce-6457-44a7-9793-22ab9ef4754e</t>
-        </is>
-      </c>
       <c r="BR15" t="inlineStr">
         <is>
+          <t>19b8da63-beb4-4ec6-8ea6-102b34c50c5a</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
           <t>2026-07-14T16:41:23</t>
         </is>
       </c>
-      <c r="BU15" t="inlineStr">
+      <c r="BV15" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV15" t="inlineStr">
+      <c r="BW15" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW15" t="inlineStr">
+      <c r="BX15" t="inlineStr">
         <is>
           <t>vqNFtU5FCbU6qmGgWH2f6a</t>
         </is>
       </c>
-      <c r="BY15" t="inlineStr">
+      <c r="BZ15" t="inlineStr">
         <is>
           <t>uuid:bd4495ac-30cf-42b1-a333-5807562ae40c</t>
         </is>
       </c>
-      <c r="BZ15">
+      <c r="CA15">
         <v>14</v>
       </c>
     </row>
@@ -5265,14 +5335,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>nursery</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>nursery_msuka</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>0</t>
@@ -5305,24 +5375,24 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
           <t>shabani burhani</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>1</t>
@@ -5330,7 +5400,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -5415,49 +5485,49 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
+      <c r="AK16" t="inlineStr">
         <is>
           <t>08:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK16" t="inlineStr">
+      <c r="AL16" t="inlineStr">
         <is>
           <t>16:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL16" t="inlineStr">
+      <c r="AM16" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
+      <c r="AN16" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
+      <c r="AO16" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr">
+      <c r="AP16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AP16" t="inlineStr">
+      <c r="AQ16" t="inlineStr">
         <is>
           <t>cleaning_and_maintaining</t>
         </is>
       </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR16" t="inlineStr">
         <is>
           <t>0</t>
@@ -5470,44 +5540,44 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="BE16" t="inlineStr">
+      <c r="BF16" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="BF16" t="inlineStr">
+      <c r="BG16" t="inlineStr">
         <is>
           <t>15271</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr">
+      <c r="BH16" t="inlineStr">
         <is>
           <t>5373</t>
         </is>
       </c>
-      <c r="BH16" t="inlineStr">
+      <c r="BI16" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="BI16" t="inlineStr">
+      <c r="BJ16" t="inlineStr">
         <is>
           <t>3120</t>
         </is>
       </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK16" t="inlineStr">
         <is>
           <t>0</t>
@@ -5515,48 +5585,53 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
           <t>8493</t>
         </is>
       </c>
-      <c r="BM16" t="inlineStr">
+      <c r="BN16" t="inlineStr">
         <is>
           <t>Cleaning and maintenance still going on</t>
         </is>
       </c>
-      <c r="BP16">
+      <c r="BQ16">
         <v>811005610</v>
       </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>b3f6f548-1e9b-416b-8e79-ecad7f507dca</t>
-        </is>
-      </c>
       <c r="BR16" t="inlineStr">
         <is>
+          <t>fb3041f3-6fa7-403c-a862-22d3861dac67</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
           <t>2026-07-14T16:49:50</t>
         </is>
       </c>
-      <c r="BU16" t="inlineStr">
+      <c r="BV16" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV16" t="inlineStr">
+      <c r="BW16" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW16" t="inlineStr">
+      <c r="BX16" t="inlineStr">
         <is>
           <t>vqNFtU5FCbU6qmGgWH2f6a</t>
         </is>
       </c>
-      <c r="BY16" t="inlineStr">
+      <c r="BZ16" t="inlineStr">
         <is>
           <t>uuid:f191c12a-4e8f-43e7-b2b8-3bed3721c320</t>
         </is>
       </c>
-      <c r="BZ16">
+      <c r="CA16">
         <v>15</v>
       </c>
     </row>
@@ -5583,14 +5658,14 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>transplanting</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>transplanting_msuka_panga_punge</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>0</t>
@@ -5628,19 +5703,19 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
           <t>shabani burhani</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>1</t>
@@ -5648,7 +5723,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -5733,57 +5808,57 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
+      <c r="AK17" t="inlineStr">
         <is>
           <t>07:45:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK17" t="inlineStr">
+      <c r="AL17" t="inlineStr">
         <is>
           <t>15:40:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL17" t="inlineStr">
+      <c r="AM17" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
+      <c r="AN17" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
+      <c r="AO17" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AO17" t="inlineStr">
+      <c r="AP17" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AP17" t="inlineStr">
+      <c r="AQ17" t="inlineStr">
         <is>
           <t>transplantation</t>
         </is>
       </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
@@ -5791,66 +5866,66 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AW17" t="inlineStr">
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
         <is>
           <t>520</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AY17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr">
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
+      <c r="BA17" t="inlineStr">
         <is>
           <t>520</t>
         </is>
       </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BB17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BE17" t="inlineStr">
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="BF17" t="inlineStr">
+      <c r="BG17" t="inlineStr">
         <is>
           <t>15271</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr">
+      <c r="BH17" t="inlineStr">
         <is>
           <t>6393</t>
         </is>
       </c>
-      <c r="BH17" t="inlineStr">
+      <c r="BI17" t="inlineStr">
         <is>
           <t>260</t>
         </is>
       </c>
-      <c r="BI17" t="inlineStr">
+      <c r="BJ17" t="inlineStr">
         <is>
           <t>3380</t>
         </is>
       </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK17" t="inlineStr">
         <is>
           <t>0</t>
@@ -5858,48 +5933,53 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
           <t>9773</t>
         </is>
       </c>
-      <c r="BM17" t="inlineStr">
+      <c r="BN17" t="inlineStr">
         <is>
           <t>The transplanting activities is going on</t>
         </is>
       </c>
-      <c r="BP17">
+      <c r="BQ17">
         <v>811519969</v>
       </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>abb5d1ab-e051-4862-bd5e-40c06fe89d7d</t>
-        </is>
-      </c>
       <c r="BR17" t="inlineStr">
         <is>
+          <t>d7568da5-ea67-4ae8-b58e-aa0075bebbee</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
           <t>2026-07-15T08:37:59</t>
         </is>
       </c>
-      <c r="BU17" t="inlineStr">
+      <c r="BV17" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV17" t="inlineStr">
+      <c r="BW17" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW17" t="inlineStr">
+      <c r="BX17" t="inlineStr">
         <is>
           <t>vU7fWA2ufbhKeAhbVCM2aR</t>
         </is>
       </c>
-      <c r="BY17" t="inlineStr">
+      <c r="BZ17" t="inlineStr">
         <is>
           <t>uuid:abb5d1ab-e051-4862-bd5e-40c06fe89d7d</t>
         </is>
       </c>
-      <c r="BZ17">
+      <c r="CA17">
         <v>16</v>
       </c>
     </row>
@@ -5926,14 +6006,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>nursery</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>nursery_msuka</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>0</t>
@@ -5966,24 +6046,24 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
           <t>shabani burhani</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>1</t>
@@ -5991,7 +6071,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -6076,52 +6156,52 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
+      <c r="AK18" t="inlineStr">
         <is>
           <t>08:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK18" t="inlineStr">
+      <c r="AL18" t="inlineStr">
         <is>
           <t>16:20:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL18" t="inlineStr">
+      <c r="AM18" t="inlineStr">
         <is>
           <t>rising</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
+      <c r="AN18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
+      <c r="AO18" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO18" t="inlineStr">
+      <c r="AP18" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AP18" t="inlineStr">
+      <c r="AQ18" t="inlineStr">
         <is>
           <t>fragmentation</t>
         </is>
       </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -6136,44 +6216,44 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
           <t>672</t>
         </is>
       </c>
-      <c r="AV18" t="inlineStr">
+      <c r="AW18" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="BE18" t="inlineStr">
+      <c r="BF18" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="BF18" t="inlineStr">
+      <c r="BG18" t="inlineStr">
         <is>
           <t>15943</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr">
+      <c r="BH18" t="inlineStr">
         <is>
           <t>6393</t>
         </is>
       </c>
-      <c r="BH18" t="inlineStr">
+      <c r="BI18" t="inlineStr">
         <is>
           <t>260</t>
         </is>
       </c>
-      <c r="BI18" t="inlineStr">
+      <c r="BJ18" t="inlineStr">
         <is>
           <t>3380</t>
         </is>
       </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK18" t="inlineStr">
         <is>
           <t>0</t>
@@ -6186,43 +6266,48 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
           <t>Team need epoxy and fence wire to proceed with fragmentation</t>
         </is>
       </c>
-      <c r="BP18">
+      <c r="BQ18">
         <v>811526938</v>
       </c>
-      <c r="BQ18" t="inlineStr">
-        <is>
-          <t>8fc7e36b-bd41-47eb-a1fc-d21cc96e474c</t>
-        </is>
-      </c>
       <c r="BR18" t="inlineStr">
         <is>
+          <t>cccb3ec5-8544-43dd-ab4c-a00abd0723fd</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
           <t>2026-07-15T08:44:12</t>
         </is>
       </c>
-      <c r="BU18" t="inlineStr">
+      <c r="BV18" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV18" t="inlineStr">
+      <c r="BW18" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW18" t="inlineStr">
+      <c r="BX18" t="inlineStr">
         <is>
           <t>vU7fWA2ufbhKeAhbVCM2aR</t>
         </is>
       </c>
-      <c r="BY18" t="inlineStr">
+      <c r="BZ18" t="inlineStr">
         <is>
           <t>uuid:8fc7e36b-bd41-47eb-a1fc-d21cc96e474c</t>
         </is>
       </c>
-      <c r="BZ18">
+      <c r="CA18">
         <v>17</v>
       </c>
     </row>
@@ -6249,14 +6334,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>nursery</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>nursery_msuka</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>0</t>
@@ -6289,24 +6374,24 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
           <t>shabani burhani</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>1</t>
@@ -6314,7 +6399,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -6399,57 +6484,57 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AJ19" t="inlineStr">
+      <c r="AK19" t="inlineStr">
         <is>
           <t>08:05:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK19" t="inlineStr">
+      <c r="AL19" t="inlineStr">
         <is>
           <t>16:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr">
+      <c r="AM19" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
+      <c r="AN19" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
+      <c r="AO19" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO19" t="inlineStr">
+      <c r="AP19" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AP19" t="inlineStr">
+      <c r="AQ19" t="inlineStr">
         <is>
           <t>transplantation</t>
         </is>
       </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
@@ -6457,66 +6542,66 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AW19" t="inlineStr">
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AY19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
+      <c r="BA19" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BB19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BE19" t="inlineStr">
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="BF19" t="inlineStr">
+      <c r="BG19" t="inlineStr">
         <is>
           <t>15463</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr">
+      <c r="BH19" t="inlineStr">
         <is>
           <t>6873</t>
         </is>
       </c>
-      <c r="BH19" t="inlineStr">
+      <c r="BI19" t="inlineStr">
         <is>
           <t>270</t>
         </is>
       </c>
-      <c r="BI19" t="inlineStr">
+      <c r="BJ19" t="inlineStr">
         <is>
           <t>3510</t>
         </is>
       </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK19" t="inlineStr">
         <is>
           <t>0</t>
@@ -6524,48 +6609,53 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
           <t>10383</t>
         </is>
       </c>
-      <c r="BM19" t="inlineStr">
+      <c r="BN19" t="inlineStr">
         <is>
           <t>I would like to report the disturbance at the coral transplantation site, we observed several ragments were no longer secured in their coral clips like 10%</t>
         </is>
       </c>
-      <c r="BP19">
+      <c r="BQ19">
         <v>811555782</v>
       </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>85f261f1-5740-4686-8d28-8a4174c0bc9f</t>
-        </is>
-      </c>
       <c r="BR19" t="inlineStr">
         <is>
+          <t>7a8c538d-8487-4174-8cbd-40cf98e65d40</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
           <t>2026-07-15T09:12:42</t>
         </is>
       </c>
-      <c r="BU19" t="inlineStr">
+      <c r="BV19" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV19" t="inlineStr">
+      <c r="BW19" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW19" t="inlineStr">
+      <c r="BX19" t="inlineStr">
         <is>
           <t>vU7fWA2ufbhKeAhbVCM2aR</t>
         </is>
       </c>
-      <c r="BY19" t="inlineStr">
+      <c r="BZ19" t="inlineStr">
         <is>
           <t>uuid:85f261f1-5740-4686-8d28-8a4174c0bc9f</t>
         </is>
       </c>
-      <c r="BZ19">
+      <c r="CA19">
         <v>18</v>
       </c>
     </row>
@@ -6592,14 +6682,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>transplanting</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>transplanting_msuka_panga_punge</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>0</t>
@@ -6637,19 +6727,19 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
           <t>shabani burhani</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>1</t>
@@ -6657,7 +6747,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -6742,57 +6832,57 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr">
+      <c r="AK20" t="inlineStr">
         <is>
           <t>08:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK20" t="inlineStr">
+      <c r="AL20" t="inlineStr">
         <is>
           <t>16:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL20" t="inlineStr">
+      <c r="AM20" t="inlineStr">
         <is>
           <t>rising</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
+      <c r="AN20" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
+      <c r="AO20" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO20" t="inlineStr">
+      <c r="AP20" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AP20" t="inlineStr">
+      <c r="AQ20" t="inlineStr">
         <is>
           <t>transplantation</t>
         </is>
       </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
@@ -6800,66 +6890,66 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AW20" t="inlineStr">
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AY20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr">
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
+      <c r="BA20" t="inlineStr">
         <is>
           <t>340</t>
         </is>
       </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BB20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BE20" t="inlineStr">
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="BF20" t="inlineStr">
+      <c r="BG20" t="inlineStr">
         <is>
           <t>15123</t>
         </is>
       </c>
-      <c r="BG20" t="inlineStr">
+      <c r="BH20" t="inlineStr">
         <is>
           <t>7210</t>
         </is>
       </c>
-      <c r="BH20" t="inlineStr">
+      <c r="BI20" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="BI20" t="inlineStr">
+      <c r="BJ20" t="inlineStr">
         <is>
           <t>3640</t>
         </is>
       </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK20" t="inlineStr">
         <is>
           <t>0</t>
@@ -6867,48 +6957,53 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
           <t>10850</t>
         </is>
       </c>
-      <c r="BM20" t="inlineStr">
+      <c r="BN20" t="inlineStr">
         <is>
           <t>The replacement activity takes place today to the disturbed corals</t>
         </is>
       </c>
-      <c r="BP20">
+      <c r="BQ20">
         <v>811564995</v>
       </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>ecf523be-a8b3-4072-a8c3-e5429ac201c1</t>
-        </is>
-      </c>
       <c r="BR20" t="inlineStr">
         <is>
+          <t>3130ddf8-123b-4465-ac63-8a84e75d470c</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
           <t>2026-07-15T09:21:05</t>
         </is>
       </c>
-      <c r="BU20" t="inlineStr">
+      <c r="BV20" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV20" t="inlineStr">
+      <c r="BW20" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW20" t="inlineStr">
+      <c r="BX20" t="inlineStr">
         <is>
           <t>vU7fWA2ufbhKeAhbVCM2aR</t>
         </is>
       </c>
-      <c r="BY20" t="inlineStr">
+      <c r="BZ20" t="inlineStr">
         <is>
           <t>uuid:ecf523be-a8b3-4072-a8c3-e5429ac201c1</t>
         </is>
       </c>
-      <c r="BZ20">
+      <c r="CA20">
         <v>19</v>
       </c>
     </row>
@@ -6935,14 +7030,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>transplanting</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>transplanting_msuka_panga_punge</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>0</t>
@@ -6980,19 +7075,19 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
           <t>shabani burhani</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>1</t>
@@ -7000,7 +7095,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -7085,57 +7180,57 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr">
+      <c r="AK21" t="inlineStr">
         <is>
           <t>08:45:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK21" t="inlineStr">
+      <c r="AL21" t="inlineStr">
         <is>
           <t>21:45:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
+      <c r="AM21" t="inlineStr">
         <is>
           <t>rising</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
+      <c r="AN21" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
+      <c r="AO21" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="AO21" t="inlineStr">
+      <c r="AP21" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AP21" t="inlineStr">
+      <c r="AQ21" t="inlineStr">
         <is>
           <t>transplantation</t>
         </is>
       </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
@@ -7143,66 +7238,66 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AW21" t="inlineStr">
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
+      <c r="AY21" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr">
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
+      <c r="BA21" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BB21" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BE21" t="inlineStr">
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="BF21" t="inlineStr">
+      <c r="BG21" t="inlineStr">
         <is>
           <t>14703</t>
         </is>
       </c>
-      <c r="BG21" t="inlineStr">
+      <c r="BH21" t="inlineStr">
         <is>
           <t>7603</t>
         </is>
       </c>
-      <c r="BH21" t="inlineStr">
+      <c r="BI21" t="inlineStr">
         <is>
           <t>290</t>
         </is>
       </c>
-      <c r="BI21" t="inlineStr">
+      <c r="BJ21" t="inlineStr">
         <is>
           <t>3770</t>
         </is>
       </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK21" t="inlineStr">
         <is>
           <t>0</t>
@@ -7210,48 +7305,53 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
           <t>11400</t>
         </is>
       </c>
-      <c r="BM21" t="inlineStr">
+      <c r="BN21" t="inlineStr">
         <is>
           <t>Team still make replacement of the disturbed coral fragments</t>
         </is>
       </c>
-      <c r="BP21">
+      <c r="BQ21">
         <v>812141286</v>
       </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>87fb6d03-8c1f-4128-9ba3-803e061d2c05</t>
-        </is>
-      </c>
       <c r="BR21" t="inlineStr">
         <is>
+          <t>7707989a-8447-4288-8cff-4373d20974c9</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
           <t>2026-07-15T18:49:33</t>
         </is>
       </c>
-      <c r="BU21" t="inlineStr">
+      <c r="BV21" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV21" t="inlineStr">
+      <c r="BW21" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW21" t="inlineStr">
+      <c r="BX21" t="inlineStr">
         <is>
           <t>vU7fWA2ufbhKeAhbVCM2aR</t>
         </is>
       </c>
-      <c r="BY21" t="inlineStr">
+      <c r="BZ21" t="inlineStr">
         <is>
           <t>uuid:87fb6d03-8c1f-4128-9ba3-803e061d2c05</t>
         </is>
       </c>
-      <c r="BZ21">
+      <c r="CA21">
         <v>20</v>
       </c>
     </row>
@@ -7278,22 +7378,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>transplanting</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>transplanting_kirui_shangani</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -7328,14 +7428,14 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
           <t>phares adam yusuf omary nusra pagu hemeduni_abdalla</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>0</t>
@@ -7343,7 +7443,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -7368,7 +7468,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -7383,12 +7483,12 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -7418,7 +7518,7 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -7428,57 +7528,57 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
+      <c r="AK22" t="inlineStr">
         <is>
           <t>09:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK22" t="inlineStr">
+      <c r="AL22" t="inlineStr">
         <is>
           <t>13:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL22" t="inlineStr">
+      <c r="AM22" t="inlineStr">
         <is>
           <t>falling</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
+      <c r="AN22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
+      <c r="AO22" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO22" t="inlineStr">
+      <c r="AP22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AP22" t="inlineStr">
+      <c r="AQ22" t="inlineStr">
         <is>
           <t>transplantation</t>
         </is>
       </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
@@ -7486,16 +7586,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AW22" t="inlineStr">
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
         <is>
           <t>344</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>0</t>
@@ -7508,98 +7608,103 @@
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
           <t>344</t>
         </is>
       </c>
-      <c r="BE22" t="inlineStr">
+      <c r="BF22" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="BF22" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>11248</t>
         </is>
       </c>
-      <c r="BG22" t="inlineStr">
+      <c r="BH22" t="inlineStr">
         <is>
           <t>2249</t>
         </is>
       </c>
-      <c r="BH22" t="inlineStr">
+      <c r="BI22" t="inlineStr">
         <is>
           <t>305</t>
         </is>
       </c>
-      <c r="BI22" t="inlineStr">
+      <c r="BJ22" t="inlineStr">
         <is>
           <t>3965</t>
         </is>
       </c>
-      <c r="BJ22" t="inlineStr">
+      <c r="BK22" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="BK22" t="inlineStr">
+      <c r="BL22" t="inlineStr">
         <is>
           <t>4022</t>
         </is>
       </c>
-      <c r="BL22" t="inlineStr">
+      <c r="BM22" t="inlineStr">
         <is>
           <t>10236</t>
         </is>
       </c>
-      <c r="BM22" t="inlineStr">
+      <c r="BN22" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="BN22" t="inlineStr">
+      <c r="BO22" t="inlineStr">
         <is>
           <t>P5130349-19_47_28.JPG</t>
         </is>
       </c>
-      <c r="BP22">
+      <c r="BQ22">
         <v>813127665</v>
       </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>a0a95e17-922f-4b43-ac4a-e59c3322e00e</t>
-        </is>
-      </c>
       <c r="BR22" t="inlineStr">
         <is>
+          <t>a62913b5-b69f-48c1-b0a1-ee5d470e9507</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
           <t>2026-07-16T16:47:44</t>
         </is>
       </c>
-      <c r="BU22" t="inlineStr">
+      <c r="BV22" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV22" t="inlineStr">
+      <c r="BW22" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW22" t="inlineStr">
+      <c r="BX22" t="inlineStr">
         <is>
           <t>vU7fWA2ufbhKeAhbVCM2aR</t>
         </is>
       </c>
-      <c r="BY22" t="inlineStr">
+      <c r="BZ22" t="inlineStr">
         <is>
           <t>uuid:a0a95e17-922f-4b43-ac4a-e59c3322e00e</t>
         </is>
       </c>
-      <c r="BZ22">
+      <c r="CA22">
         <v>21</v>
       </c>
     </row>
@@ -7626,14 +7731,14 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>transplanting</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>transplanting_msuka_panga_punge</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>0</t>
@@ -7671,19 +7776,19 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
           <t>shabani burhani</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>1</t>
@@ -7691,7 +7796,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -7776,57 +7881,57 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
+      <c r="AK23" t="inlineStr">
         <is>
           <t>20:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK23" t="inlineStr">
+      <c r="AL23" t="inlineStr">
         <is>
           <t>15:30:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
+      <c r="AM23" t="inlineStr">
         <is>
           <t>rising</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
+      <c r="AN23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
+      <c r="AO23" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="AO23" t="inlineStr">
+      <c r="AP23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AP23" t="inlineStr">
+      <c r="AQ23" t="inlineStr">
         <is>
           <t>transplantation</t>
         </is>
       </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
@@ -7834,66 +7939,66 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AW23" t="inlineStr">
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AY23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr">
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
+      <c r="BA23" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BB23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="BE23" t="inlineStr">
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="BF23" t="inlineStr">
+      <c r="BG23" t="inlineStr">
         <is>
           <t>14283</t>
         </is>
       </c>
-      <c r="BG23" t="inlineStr">
+      <c r="BH23" t="inlineStr">
         <is>
           <t>8023</t>
         </is>
       </c>
-      <c r="BH23" t="inlineStr">
+      <c r="BI23" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="BI23" t="inlineStr">
+      <c r="BJ23" t="inlineStr">
         <is>
           <t>3900</t>
         </is>
       </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK23" t="inlineStr">
         <is>
           <t>0</t>
@@ -7901,48 +8006,53 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
           <t>11923</t>
         </is>
       </c>
-      <c r="BM23" t="inlineStr">
+      <c r="BN23" t="inlineStr">
         <is>
           <t>Team need epoxy for the fragmentation</t>
         </is>
       </c>
-      <c r="BP23">
+      <c r="BQ23">
         <v>813166498</v>
       </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>fb98aa79-7388-40d5-9359-40215b1ac838</t>
-        </is>
-      </c>
       <c r="BR23" t="inlineStr">
         <is>
+          <t>5f4e9038-cf5c-48cc-99b7-05ecb6035a5d</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
           <t>2026-07-16T17:21:36</t>
         </is>
       </c>
-      <c r="BU23" t="inlineStr">
+      <c r="BV23" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV23" t="inlineStr">
+      <c r="BW23" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW23" t="inlineStr">
+      <c r="BX23" t="inlineStr">
         <is>
           <t>vU7fWA2ufbhKeAhbVCM2aR</t>
         </is>
       </c>
-      <c r="BY23" t="inlineStr">
+      <c r="BZ23" t="inlineStr">
         <is>
           <t>uuid:fb98aa79-7388-40d5-9359-40215b1ac838</t>
         </is>
       </c>
-      <c r="BZ23">
+      <c r="CA23">
         <v>22</v>
       </c>
     </row>
@@ -7969,14 +8079,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>nursery</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>nursery_msuka</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>0</t>
@@ -8009,24 +8119,24 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
           <t>shabani burhani</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>1</t>
@@ -8034,7 +8144,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -8119,49 +8229,49 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
+      <c r="AK24" t="inlineStr">
         <is>
           <t>07:15:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK24" t="inlineStr">
+      <c r="AL24" t="inlineStr">
         <is>
           <t>12:05:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
+      <c r="AM24" t="inlineStr">
         <is>
           <t>falling</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AN24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AO24" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO24" t="inlineStr">
+      <c r="AP24" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AP24" t="inlineStr">
+      <c r="AQ24" t="inlineStr">
         <is>
           <t>cleaning_and_maintaining</t>
         </is>
       </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR24" t="inlineStr">
         <is>
           <t>0</t>
@@ -8174,44 +8284,44 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BD24" t="inlineStr">
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="BE24" t="inlineStr">
+      <c r="BF24" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="BF24" t="inlineStr">
+      <c r="BG24" t="inlineStr">
         <is>
           <t>14283</t>
         </is>
       </c>
-      <c r="BG24" t="inlineStr">
+      <c r="BH24" t="inlineStr">
         <is>
           <t>8023</t>
         </is>
       </c>
-      <c r="BH24" t="inlineStr">
+      <c r="BI24" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="BI24" t="inlineStr">
+      <c r="BJ24" t="inlineStr">
         <is>
           <t>3900</t>
         </is>
       </c>
-      <c r="BJ24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BK24" t="inlineStr">
         <is>
           <t>0</t>
@@ -8219,48 +8329,53 @@
       </c>
       <c r="BL24" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
           <t>11923</t>
         </is>
       </c>
-      <c r="BM24" t="inlineStr">
+      <c r="BN24" t="inlineStr">
         <is>
           <t>Team also went to take COO</t>
         </is>
       </c>
-      <c r="BP24">
+      <c r="BQ24">
         <v>814289828</v>
       </c>
-      <c r="BQ24" t="inlineStr">
-        <is>
-          <t>201f8009-f81e-4c91-99b0-590c647f9d9f</t>
-        </is>
-      </c>
       <c r="BR24" t="inlineStr">
         <is>
+          <t>847968b4-2a3f-4a4f-8c15-96ab4aff16f8</t>
+        </is>
+      </c>
+      <c r="BS24" t="inlineStr">
+        <is>
           <t>2026-07-17T18:09:47</t>
         </is>
       </c>
-      <c r="BU24" t="inlineStr">
+      <c r="BV24" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV24" t="inlineStr">
+      <c r="BW24" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW24" t="inlineStr">
+      <c r="BX24" t="inlineStr">
         <is>
           <t>vU7fWA2ufbhKeAhbVCM2aR</t>
         </is>
       </c>
-      <c r="BY24" t="inlineStr">
+      <c r="BZ24" t="inlineStr">
         <is>
           <t>uuid:201f8009-f81e-4c91-99b0-590c647f9d9f</t>
         </is>
       </c>
-      <c r="BZ24">
+      <c r="CA24">
         <v>23</v>
       </c>
     </row>
@@ -8287,22 +8402,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>transplanting</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>transplanting_kirui_shangani</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -8337,14 +8452,14 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
           <t>phares adam yusuf omary nusra pagu hemeduni_abdalla</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>0</t>
@@ -8352,7 +8467,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -8377,7 +8492,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -8392,12 +8507,12 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -8427,67 +8542,67 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
+      <c r="AK25" t="inlineStr">
         <is>
           <t>09:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AK25" t="inlineStr">
+      <c r="AL25" t="inlineStr">
         <is>
           <t>14:00:00.000+03:00</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
+      <c r="AM25" t="inlineStr">
         <is>
           <t>falling</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AN25" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
+      <c r="AO25" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="AO25" t="inlineStr">
+      <c r="AP25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AP25" t="inlineStr">
+      <c r="AQ25" t="inlineStr">
         <is>
           <t>transplantation</t>
         </is>
       </c>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
@@ -8495,16 +8610,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AW25" t="inlineStr">
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
         <is>
           <t>232</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>0</t>
@@ -8517,98 +8632,103 @@
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="BE25" t="inlineStr">
+      <c r="BF25" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="BF25" t="inlineStr">
+      <c r="BG25" t="inlineStr">
         <is>
           <t>11248</t>
         </is>
       </c>
-      <c r="BG25" t="inlineStr">
+      <c r="BH25" t="inlineStr">
         <is>
           <t>2249</t>
         </is>
       </c>
-      <c r="BH25" t="inlineStr">
+      <c r="BI25" t="inlineStr">
         <is>
           <t>305</t>
         </is>
       </c>
-      <c r="BI25" t="inlineStr">
+      <c r="BJ25" t="inlineStr">
         <is>
           <t>3965</t>
         </is>
       </c>
-      <c r="BJ25" t="inlineStr">
+      <c r="BK25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="BK25" t="inlineStr">
+      <c r="BL25" t="inlineStr">
         <is>
           <t>4254</t>
         </is>
       </c>
-      <c r="BL25" t="inlineStr">
+      <c r="BM25" t="inlineStr">
         <is>
           <t>10468</t>
         </is>
       </c>
-      <c r="BM25" t="inlineStr">
+      <c r="BN25" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="BN25" t="inlineStr">
+      <c r="BO25" t="inlineStr">
         <is>
           <t>P5130345-20_23_50.JPG</t>
         </is>
       </c>
-      <c r="BP25">
+      <c r="BQ25">
         <v>814961031</v>
       </c>
-      <c r="BQ25" t="inlineStr">
-        <is>
-          <t>859457e0-fd06-4450-947a-aa082af93f13</t>
-        </is>
-      </c>
       <c r="BR25" t="inlineStr">
         <is>
+          <t>79ad2513-3ff4-42ce-a7ab-6c8b67c7505f</t>
+        </is>
+      </c>
+      <c r="BS25" t="inlineStr">
+        <is>
           <t>2026-07-18T17:24:17</t>
         </is>
       </c>
-      <c r="BU25" t="inlineStr">
+      <c r="BV25" t="inlineStr">
         <is>
           <t>submitted_via_web</t>
         </is>
       </c>
-      <c r="BV25" t="inlineStr">
+      <c r="BW25" t="inlineStr">
         <is>
           <t>wcs_tanzania</t>
         </is>
       </c>
-      <c r="BW25" t="inlineStr">
+      <c r="BX25" t="inlineStr">
         <is>
           <t>vU7fWA2ufbhKeAhbVCM2aR</t>
         </is>
       </c>
-      <c r="BY25" t="inlineStr">
+      <c r="BZ25" t="inlineStr">
         <is>
           <t>uuid:3e7d8c3a-19f6-4f93-9070-2e3c40090d32</t>
         </is>
       </c>
-      <c r="BZ25">
+      <c r="CA25">
         <v>24</v>
       </c>
     </row>
